--- a/Archival/Pepper/remarks.xlsx
+++ b/Archival/Pepper/remarks.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohamed.Tharif B\Documents\MSSQL\Pepper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohamed.Tharif B\Documents\MSSQL\Archival\Pepper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8317977-FA1A-4D7F-A69D-EC78CFE270A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927784FA-7E6A-4148-B395-AED4775AA38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D5FB169B-0A45-4A04-8E8C-3FD898E5EAFF}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D5FB169B-0A45-4A04-8E8C-3FD898E5EAFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="116">
   <si>
     <t>SourceTable</t>
   </si>
@@ -301,6 +302,105 @@
   </si>
   <si>
     <t>Everyday</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>Table Name</t>
+  </si>
+  <si>
+    <t>Bankstatementtransactoindetailsvalidate</t>
+  </si>
+  <si>
+    <t>BAnkstatementValidate</t>
+  </si>
+  <si>
+    <t>BankstatementTransactiondetails</t>
+  </si>
+  <si>
+    <t>Bankstatement</t>
+  </si>
+  <si>
+    <t>CallBackPostServiceLog</t>
+  </si>
+  <si>
+    <t>Ruleservicelog</t>
+  </si>
+  <si>
+    <t>MerchantURLLogDetails</t>
+  </si>
+  <si>
+    <t>DocumentManual</t>
+  </si>
+  <si>
+    <t>DocumentValidatingMessages</t>
+  </si>
+  <si>
+    <t>TimeAnalysis</t>
+  </si>
+  <si>
+    <t>DeletedDocumentDetails</t>
+  </si>
+  <si>
+    <t>ApplicantMaster</t>
+  </si>
+  <si>
+    <t>Applicationcustomdata</t>
+  </si>
+  <si>
+    <t>LgLog</t>
+  </si>
+  <si>
+    <t>MerchantResponseDetails</t>
+  </si>
+  <si>
+    <t>ReverseApi</t>
+  </si>
+  <si>
+    <t>AppAllocation</t>
+  </si>
+  <si>
+    <t>WebAPIRequest</t>
+  </si>
+  <si>
+    <t>DocumentRuleMessages-everymonth10th</t>
+  </si>
+  <si>
+    <t>OCRServiceLog</t>
+  </si>
+  <si>
+    <t>Autosampling</t>
+  </si>
+  <si>
+    <t>AutoDataEntryserviceLog</t>
+  </si>
+  <si>
+    <t>Applications</t>
+  </si>
+  <si>
+    <t>ITRTransactionDetails</t>
+  </si>
+  <si>
+    <t>ITR</t>
+  </si>
+  <si>
+    <t>ITRValidateTransactionDetails</t>
+  </si>
+  <si>
+    <t>ITRValidate</t>
+  </si>
+  <si>
+    <t>Form16ValidateTrasactionDetails</t>
+  </si>
+  <si>
+    <t>Form16Validate</t>
+  </si>
+  <si>
+    <t>Form16TrasactionDetails</t>
+  </si>
+  <si>
+    <t>Form16</t>
   </si>
 </sst>
 </file>
@@ -1235,4 +1335,274 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25256D2-14F6-4283-B508-5C7FA48ADE98}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>